--- a/Phenotype/Tables/EPS_TableS9A_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS9A_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,22 +362,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Df</t>
+          <t>Sum Sq</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>Mean Sq</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>NumDF</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DenDF</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>F value</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pr(&gt;F)</t>
         </is>
       </c>
     </row>
@@ -387,22 +397,32 @@
           <t>Morphology</t>
         </is>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.634</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>2.634</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.765</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.097</t>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>113.497856581655</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5.226</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.024</t>
         </is>
       </c>
     </row>
@@ -412,22 +432,32 @@
           <t>Variety</t>
         </is>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.243</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.701</t>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>248.52423504245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.233</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.293</t>
         </is>
       </c>
     </row>
@@ -437,22 +467,32 @@
           <t>PC1</t>
         </is>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5.707</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.215</t>
+          <t>5.707</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.191</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>&lt; 0.001</t>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>112.931184118731</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>11.325</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -462,20 +502,30 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8.889</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.240</t>
+          <t>8.889</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32.993</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>112.9311840928817</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>17.640</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -484,45 +534,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Morphology:Variety</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2</v>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6.821</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>0.974</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.238</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.108</t>
+          <t>7.000</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>1989.392188432444</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.061</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Residuals</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>343</v>
+          <t>Morphology:Variety</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.425</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>96.066</t>
+          <t>1.712</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>229.4318375522018</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3.398</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.035</t>
         </is>
       </c>
     </row>

--- a/Phenotype/Tables/EPS_TableS9A_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS9A_FromR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,25 +367,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mean Sq</t>
+          <t>Df</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NumDF</t>
+          <t>F value</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DenDF</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>F value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pr(&gt;F)</t>
         </is>
@@ -399,30 +389,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.634</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2.634</t>
-        </is>
+          <t>2.465</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>113.497856581655</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5.226</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.024</t>
+          <t>8.802</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.003</t>
         </is>
       </c>
     </row>
@@ -434,30 +414,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.243</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.621</t>
-        </is>
+          <t>0.199</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>248.52423504245</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1.233</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.293</t>
+          <t>0.356</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.701</t>
         </is>
       </c>
     </row>
@@ -469,30 +439,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.707</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5.707</t>
-        </is>
+          <t>6.459</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>112.931184118731</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>11.325</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.001</t>
+          <t>23.062</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt; 0.001</t>
         </is>
       </c>
     </row>
@@ -504,28 +464,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.889</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8.889</t>
-        </is>
+          <t>9.240</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>112.9311840928817</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>17.640</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>32.993</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>&lt; 0.001</t>
         </is>
@@ -534,70 +484,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>Morphology:Variety</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.821</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.974</t>
-        </is>
+          <t>1.254</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.000</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>1989.392188432444</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.061</t>
+          <t>2.238</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Morphology:Variety</t>
+          <t>Residuals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.425</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1.712</t>
-        </is>
+          <t>96.066</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>229.4318375522018</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3.398</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.035</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
